--- a/reports/Test_Result_Report.xlsx
+++ b/reports/Test_Result_Report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,43 @@
         <is>
           <t>Profit BI vs DB</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Germain</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>55391759.79</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31587437.29</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <f>D3=F3</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>E3=G3</f>
+        <v/>
       </c>
     </row>
   </sheetData>
